--- a/data-manipulation-scripts/sheets-cleanup/sheets/SENSOR VELOCIDADE.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/sheets/SENSOR VELOCIDADE.xlsx
@@ -28,37 +28,37 @@
     <t>602883768956</t>
   </si>
   <si>
-    <t>SENSOR VELOC IRON TITAN CG FAN150 2014 A 2015 189044</t>
+    <t>SENSOR VELOCIDADE  IRON TITAN CG FAN150 2014 A 2015 189044</t>
   </si>
   <si>
     <t>602883768918</t>
   </si>
   <si>
-    <t>SENSOR VELOC IRON YS250 FAZER/ LANDER XTZ250/ TENERE/ LANDER ABS 189036</t>
+    <t>SENSOR VELOCIDADE  IRON YS250 FAZER/ LANDER XTZ250/ TENERE/ LANDER ABS 189036</t>
   </si>
   <si>
     <t>602883768901</t>
   </si>
   <si>
-    <t>SENSOR VELOC IRON YBR125I 2017 A 2019/ FACTOR150 2016 A 2019/ XTZ150/ FAZER150 189034</t>
+    <t>SENSOR VELOCIDADE  IRON YBR125I 2017 A 2019/ FACTOR150 2016 A 2019/ XTZ150/ FAZER150 189034</t>
   </si>
   <si>
     <t>602883768895</t>
   </si>
   <si>
-    <t>SENSOR VELOC IRON CB500F/ CBR500/ CB500/ PCX150 189032</t>
+    <t>SENSOR VELOCIDADE  IRON CB500F/ CBR500/ CB500/ PCX150 189032</t>
   </si>
   <si>
     <t>7909201059875</t>
   </si>
   <si>
-    <t>SENSOR VELOC CONDOR NXR150-160/ XRE190 2016 1102119</t>
+    <t>SENSOR VELOCIDADE  CONDOR NXR150-160/ XRE190 2016 1102119</t>
   </si>
   <si>
     <t>7908305622107</t>
   </si>
   <si>
-    <t>SENSOR VELOC MHX TITAN FAN160 2014 A 2015/ FAN125 2014 A 2015</t>
+    <t>SENSOR VELOCIDADE  MHX TITAN FAN160 2014 A 2015/ FAN125 2014 A 2015</t>
   </si>
 </sst>
 </file>
@@ -116,10 +116,10 @@
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment vertical="bottom"/>
+      <alignment horizontal="center" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -386,34 +386,34 @@
       <c r="B2" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="4">
+      <c r="C2" s="5">
         <v>2.0</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="5">
         <v>120.0</v>
       </c>
-      <c r="E2" s="5"/>
-      <c r="F2" s="5"/>
-      <c r="G2" s="5"/>
-      <c r="H2" s="5"/>
-      <c r="I2" s="5"/>
-      <c r="J2" s="5"/>
-      <c r="K2" s="5"/>
-      <c r="L2" s="5"/>
-      <c r="M2" s="5"/>
-      <c r="N2" s="5"/>
-      <c r="O2" s="5"/>
-      <c r="P2" s="5"/>
-      <c r="Q2" s="5"/>
-      <c r="R2" s="5"/>
-      <c r="S2" s="5"/>
-      <c r="T2" s="5"/>
-      <c r="U2" s="5"/>
-      <c r="V2" s="5"/>
-      <c r="W2" s="5"/>
-      <c r="X2" s="5"/>
-      <c r="Y2" s="5"/>
-      <c r="Z2" s="5"/>
+      <c r="E2" s="6"/>
+      <c r="F2" s="6"/>
+      <c r="G2" s="6"/>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6"/>
+      <c r="J2" s="6"/>
+      <c r="K2" s="6"/>
+      <c r="L2" s="6"/>
+      <c r="M2" s="6"/>
+      <c r="N2" s="6"/>
+      <c r="O2" s="6"/>
+      <c r="P2" s="6"/>
+      <c r="Q2" s="6"/>
+      <c r="R2" s="6"/>
+      <c r="S2" s="6"/>
+      <c r="T2" s="6"/>
+      <c r="U2" s="6"/>
+      <c r="V2" s="6"/>
+      <c r="W2" s="6"/>
+      <c r="X2" s="6"/>
+      <c r="Y2" s="6"/>
+      <c r="Z2" s="6"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
@@ -422,32 +422,34 @@
       <c r="B3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="4">
+      <c r="C3" s="5">
         <v>2.0</v>
       </c>
-      <c r="D3" s="6"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="5"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="5"/>
-      <c r="K3" s="5"/>
-      <c r="L3" s="5"/>
-      <c r="M3" s="5"/>
-      <c r="N3" s="5"/>
-      <c r="O3" s="5"/>
-      <c r="P3" s="5"/>
-      <c r="Q3" s="5"/>
-      <c r="R3" s="5"/>
-      <c r="S3" s="5"/>
-      <c r="T3" s="5"/>
-      <c r="U3" s="5"/>
-      <c r="V3" s="5"/>
-      <c r="W3" s="5"/>
-      <c r="X3" s="5"/>
-      <c r="Y3" s="5"/>
-      <c r="Z3" s="5"/>
+      <c r="D3" s="4">
+        <v>130.0</v>
+      </c>
+      <c r="E3" s="6"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="6"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="6"/>
+      <c r="J3" s="6"/>
+      <c r="K3" s="6"/>
+      <c r="L3" s="6"/>
+      <c r="M3" s="6"/>
+      <c r="N3" s="6"/>
+      <c r="O3" s="6"/>
+      <c r="P3" s="6"/>
+      <c r="Q3" s="6"/>
+      <c r="R3" s="6"/>
+      <c r="S3" s="6"/>
+      <c r="T3" s="6"/>
+      <c r="U3" s="6"/>
+      <c r="V3" s="6"/>
+      <c r="W3" s="6"/>
+      <c r="X3" s="6"/>
+      <c r="Y3" s="6"/>
+      <c r="Z3" s="6"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
@@ -456,40 +458,40 @@
       <c r="B4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="4">
+      <c r="C4" s="5">
         <v>4.0</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="5">
         <v>130.0</v>
       </c>
-      <c r="E4" s="5"/>
-      <c r="F4" s="5"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="5"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="5"/>
-      <c r="K4" s="5"/>
-      <c r="L4" s="5"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="5"/>
-      <c r="Q4" s="5"/>
-      <c r="R4" s="5"/>
-      <c r="S4" s="5"/>
-      <c r="T4" s="5"/>
-      <c r="U4" s="5"/>
-      <c r="V4" s="5"/>
-      <c r="W4" s="5"/>
-      <c r="X4" s="5"/>
-      <c r="Y4" s="5"/>
-      <c r="Z4" s="5"/>
+      <c r="E4" s="6"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="6"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="6"/>
+      <c r="J4" s="6"/>
+      <c r="K4" s="6"/>
+      <c r="L4" s="6"/>
+      <c r="M4" s="6"/>
+      <c r="N4" s="6"/>
+      <c r="O4" s="6"/>
+      <c r="P4" s="6"/>
+      <c r="Q4" s="6"/>
+      <c r="R4" s="6"/>
+      <c r="S4" s="6"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="6"/>
+      <c r="V4" s="6"/>
+      <c r="W4" s="6"/>
+      <c r="X4" s="6"/>
+      <c r="Y4" s="6"/>
+      <c r="Z4" s="6"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="7" t="s">
+      <c r="B5" s="4" t="s">
         <v>11</v>
       </c>
       <c r="C5" s="7">
@@ -498,68 +500,70 @@
       <c r="D5" s="7">
         <v>120.0</v>
       </c>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="5"/>
-      <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="5"/>
-      <c r="Q5" s="5"/>
-      <c r="R5" s="5"/>
-      <c r="S5" s="5"/>
-      <c r="T5" s="5"/>
-      <c r="U5" s="5"/>
-      <c r="V5" s="5"/>
-      <c r="W5" s="5"/>
-      <c r="X5" s="5"/>
-      <c r="Y5" s="5"/>
-      <c r="Z5" s="5"/>
+      <c r="E5" s="6"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="6"/>
+      <c r="L5" s="6"/>
+      <c r="M5" s="6"/>
+      <c r="N5" s="6"/>
+      <c r="O5" s="6"/>
+      <c r="P5" s="6"/>
+      <c r="Q5" s="6"/>
+      <c r="R5" s="6"/>
+      <c r="S5" s="6"/>
+      <c r="T5" s="6"/>
+      <c r="U5" s="6"/>
+      <c r="V5" s="6"/>
+      <c r="W5" s="6"/>
+      <c r="X5" s="6"/>
+      <c r="Y5" s="6"/>
+      <c r="Z5" s="6"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="4" t="s">
         <v>13</v>
       </c>
       <c r="C6" s="7">
         <v>1.0</v>
       </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="5"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-      <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
-      <c r="R6" s="5"/>
-      <c r="S6" s="5"/>
-      <c r="T6" s="5"/>
-      <c r="U6" s="5"/>
-      <c r="V6" s="5"/>
-      <c r="W6" s="5"/>
-      <c r="X6" s="5"/>
-      <c r="Y6" s="5"/>
-      <c r="Z6" s="5"/>
+      <c r="D6" s="4">
+        <v>140.0</v>
+      </c>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="6"/>
+      <c r="L6" s="6"/>
+      <c r="M6" s="6"/>
+      <c r="N6" s="6"/>
+      <c r="O6" s="6"/>
+      <c r="P6" s="6"/>
+      <c r="Q6" s="6"/>
+      <c r="R6" s="6"/>
+      <c r="S6" s="6"/>
+      <c r="T6" s="6"/>
+      <c r="U6" s="6"/>
+      <c r="V6" s="6"/>
+      <c r="W6" s="6"/>
+      <c r="X6" s="6"/>
+      <c r="Y6" s="6"/>
+      <c r="Z6" s="6"/>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="B7" s="7" t="s">
+      <c r="B7" s="4" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="7">
@@ -568,28 +572,28 @@
       <c r="D7" s="7">
         <v>167.0</v>
       </c>
-      <c r="E7" s="5"/>
-      <c r="F7" s="5"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-      <c r="K7" s="5"/>
-      <c r="L7" s="5"/>
-      <c r="M7" s="5"/>
-      <c r="N7" s="5"/>
-      <c r="O7" s="5"/>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
-      <c r="R7" s="5"/>
-      <c r="S7" s="5"/>
-      <c r="T7" s="5"/>
-      <c r="U7" s="5"/>
-      <c r="V7" s="5"/>
-      <c r="W7" s="5"/>
-      <c r="X7" s="5"/>
-      <c r="Y7" s="5"/>
-      <c r="Z7" s="5"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="6"/>
+      <c r="H7" s="6"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="6"/>
+      <c r="L7" s="6"/>
+      <c r="M7" s="6"/>
+      <c r="N7" s="6"/>
+      <c r="O7" s="6"/>
+      <c r="P7" s="6"/>
+      <c r="Q7" s="6"/>
+      <c r="R7" s="6"/>
+      <c r="S7" s="6"/>
+      <c r="T7" s="6"/>
+      <c r="U7" s="6"/>
+      <c r="V7" s="6"/>
+      <c r="W7" s="6"/>
+      <c r="X7" s="6"/>
+      <c r="Y7" s="6"/>
+      <c r="Z7" s="6"/>
     </row>
     <row r="8">
       <c r="A8" s="8"/>
